--- a/artfynd/A 29117-2025 artfynd.xlsx
+++ b/artfynd/A 29117-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126421790</v>
+        <v>126421146</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498645</v>
+        <v>498661</v>
       </c>
       <c r="R2" t="n">
-        <v>7007788</v>
+        <v>7007778</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 300 plantor av knärot inom ca 3 m2 yta i gallrad barrskog med inslag av björk.</t>
+          <t>1 planta med blomställning i gallrad yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126421146</v>
+        <v>126420259</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,56 +822,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bullerbäcken, Bullerbäcken, Jmt</t>
+          <t>Storflobäcken, Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498661</v>
+        <v>498815</v>
       </c>
       <c r="R3" t="n">
-        <v>7007778</v>
+        <v>7007801</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 planta med blomställning i gallrad yngre skog.</t>
+          <t>I yngre gallrad barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126420259</v>
+        <v>126422274</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>97230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,42 +944,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storflobäcken, Storflobäcken, Jmt</t>
+          <t>Bullerbäcken, Bullerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498815</v>
+        <v>498691</v>
       </c>
       <c r="R4" t="n">
-        <v>7007801</v>
+        <v>7007767</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I yngre gallrad barrskog.</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1027,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1069,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126422274</v>
+        <v>126419418</v>
       </c>
       <c r="B5" t="n">
-        <v>97230</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,37 +1056,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bullerbäcken, Bullerbäcken, Jmt</t>
+          <t>Storflobäcken, Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498691</v>
+        <v>499239</v>
       </c>
       <c r="R5" t="n">
-        <v>7007767</v>
+        <v>7007763</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gallrad yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,53 +1167,67 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126419418</v>
+        <v>126421790</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflobäcken, Storflobäcken, Jmt</t>
+          <t>Bullerbäcken, Bullerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499239</v>
+        <v>498645</v>
       </c>
       <c r="R6" t="n">
-        <v>7007763</v>
+        <v>7007788</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gallrad yngre skog.</t>
+          <t>Minst 300 plantor av knärot inom ca 3 m2 yta i gallrad barrskog med inslag av björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498649</v>
+        <v>498655</v>
       </c>
       <c r="R7" t="n">
-        <v>7007800</v>
+        <v>7007790</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 29117-2025 artfynd.xlsx
+++ b/artfynd/A 29117-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126421146</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>126420259</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>126422274</v>
       </c>
       <c r="B4" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>126419418</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>126421790</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>126421431</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
